--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91CB0FB-BD75-4D40-8B15-11837B6649D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B468FBD-EEBF-4AA0-AE80-00A856425966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>209</v>
+        <v>272</v>
       </c>
       <c r="C2" s="4">
-        <v>195</v>
+        <v>346</v>
       </c>
       <c r="D2" s="9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E2" s="13">
-        <v>5.2</v>
+        <v>5.4285714285714288</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="C3" s="4">
-        <v>194</v>
+        <v>375</v>
       </c>
       <c r="D3" s="9">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" s="13">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="C4" s="4">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="D4" s="9">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E4" s="13">
-        <v>6.4</v>
+        <v>6.1428571428571432</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="C5" s="4">
-        <v>160</v>
+        <v>226</v>
       </c>
       <c r="D5" s="9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E5" s="13">
-        <v>2.2000000000000002</v>
+        <v>2.1428571428571428</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="C6" s="4">
-        <v>263</v>
+        <v>429</v>
       </c>
       <c r="D6" s="9">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E6" s="13">
-        <v>6.2</v>
+        <v>5.7142857142857144</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="C7" s="4">
-        <v>183</v>
+        <v>360</v>
       </c>
       <c r="D7" s="9">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E7" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>258</v>
+        <v>339</v>
       </c>
       <c r="C8" s="4">
-        <v>155</v>
+        <v>307</v>
       </c>
       <c r="D8" s="9">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E8" s="13">
-        <v>9</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="C9" s="4">
-        <v>192</v>
+        <v>340</v>
       </c>
       <c r="D9" s="9">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E9" s="13">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>202</v>
+        <v>281</v>
       </c>
       <c r="C10" s="4">
-        <v>117</v>
+        <v>262</v>
       </c>
       <c r="D10" s="9">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E10" s="13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C11" s="4">
-        <v>123</v>
+        <v>225</v>
       </c>
       <c r="D11" s="9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" s="13">
-        <v>3.6</v>
+        <v>2.8571428571428572</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="C12" s="4">
-        <v>147</v>
+        <v>312</v>
       </c>
       <c r="D12" s="9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E12" s="13">
-        <v>5.2</v>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="C13" s="4">
-        <v>157</v>
+        <v>330</v>
       </c>
       <c r="D13" s="9">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E13" s="13">
-        <v>3.2</v>
+        <v>3.4285714285714284</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>179</v>
+        <v>237</v>
       </c>
       <c r="C14" s="4">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="D14" s="9">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E14" s="13">
-        <v>3.6</v>
+        <v>3.8571428571428572</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="C15" s="4">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="D15" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" s="13">
-        <v>3.8</v>
+        <v>3.4285714285714284</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="C16" s="4">
-        <v>285</v>
+        <v>442</v>
       </c>
       <c r="D16" s="9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E16" s="13">
-        <v>5</v>
+        <v>4.5714285714285712</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="C17" s="4">
-        <v>182</v>
+        <v>362</v>
       </c>
       <c r="D17" s="9">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E17" s="13">
-        <v>3.8</v>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="C18" s="4">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="D18" s="9">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E18" s="13">
-        <v>5</v>
+        <v>5.1428571428571432</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>3246</v>
+        <v>4225</v>
       </c>
       <c r="C19" s="6">
-        <v>2915</v>
+        <v>5399</v>
       </c>
       <c r="D19" s="10">
-        <v>434</v>
+        <v>578</v>
       </c>
       <c r="E19" s="14">
-        <v>5.1058823529411761</v>
+        <v>4.8571428571428568</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1116,8 +1116,12 @@
       <c r="I2" s="4">
         <v>102</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
+      <c r="J2" s="4">
+        <v>106</v>
+      </c>
+      <c r="K2" s="4">
+        <v>108</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -1170,8 +1174,12 @@
       <c r="I3" s="4">
         <v>105</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
+      <c r="J3" s="4">
+        <v>121</v>
+      </c>
+      <c r="K3" s="4">
+        <v>110</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -1224,8 +1232,12 @@
       <c r="I4" s="4">
         <v>110</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="J4" s="4">
+        <v>100</v>
+      </c>
+      <c r="K4" s="4">
+        <v>109</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -1278,8 +1290,12 @@
       <c r="I5" s="4">
         <v>101</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="J5" s="4">
+        <v>100</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -1332,8 +1348,12 @@
       <c r="I6" s="4">
         <v>120</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+      <c r="J6" s="4">
+        <v>116</v>
+      </c>
+      <c r="K6" s="4">
+        <v>112</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -1386,8 +1406,12 @@
       <c r="I7" s="4">
         <v>122</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="J7" s="4">
+        <v>125</v>
+      </c>
+      <c r="K7" s="4">
+        <v>115</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -1440,8 +1464,12 @@
       <c r="I8" s="4">
         <v>90</v>
       </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+      <c r="J8" s="4">
+        <v>117</v>
+      </c>
+      <c r="K8" s="4">
+        <v>116</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
@@ -1494,8 +1522,12 @@
       <c r="I9" s="4">
         <v>119</v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="J9" s="4">
+        <v>119</v>
+      </c>
+      <c r="K9" s="4">
+        <v>110</v>
+      </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -1548,8 +1580,12 @@
       <c r="I10" s="4">
         <v>0</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="J10" s="4">
+        <v>114</v>
+      </c>
+      <c r="K10" s="4">
+        <v>110</v>
+      </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -1602,8 +1638,12 @@
       <c r="I11" s="4">
         <v>112</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="J11" s="4">
+        <v>112</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
@@ -1656,8 +1696,12 @@
       <c r="I12" s="4">
         <v>0</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="J12" s="4">
+        <v>119</v>
+      </c>
+      <c r="K12" s="4">
+        <v>110</v>
+      </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -1710,8 +1754,12 @@
       <c r="I13" s="4">
         <v>110</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="J13" s="4">
+        <v>112</v>
+      </c>
+      <c r="K13" s="4">
+        <v>103</v>
+      </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -1764,8 +1812,12 @@
       <c r="I14" s="4">
         <v>98</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
+      <c r="J14" s="4">
+        <v>89</v>
+      </c>
+      <c r="K14" s="4">
+        <v>114</v>
+      </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -1818,8 +1870,12 @@
       <c r="I15" s="4">
         <v>131</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="J15" s="4">
+        <v>23</v>
+      </c>
+      <c r="K15" s="4">
+        <v>124</v>
+      </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -1872,8 +1928,12 @@
       <c r="I16" s="4">
         <v>111</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="J16" s="4">
+        <v>107</v>
+      </c>
+      <c r="K16" s="4">
+        <v>102</v>
+      </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -1926,8 +1986,12 @@
       <c r="I17" s="4">
         <v>125</v>
       </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="J17" s="4">
+        <v>119</v>
+      </c>
+      <c r="K17" s="4">
+        <v>113</v>
+      </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -1980,8 +2044,12 @@
       <c r="I18" s="4">
         <v>0</v>
       </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="J18" s="4">
+        <v>105</v>
+      </c>
+      <c r="K18" s="4">
+        <v>103</v>
+      </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -2034,8 +2102,12 @@
       <c r="I19" s="6">
         <v>1556</v>
       </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="J19" s="6">
+        <v>1804</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1659</v>
+      </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
@@ -2130,7 +2202,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>5.1058823529411761</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B468FBD-EEBF-4AA0-AE80-00A856425966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913A7486-A829-4FA4-AED4-684329DE30B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="C2" s="4">
-        <v>346</v>
+        <v>414</v>
       </c>
       <c r="D2" s="9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E2" s="13">
-        <v>5.4285714285714288</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="C3" s="4">
-        <v>375</v>
+        <v>549</v>
       </c>
       <c r="D3" s="9">
         <v>21</v>
       </c>
       <c r="E3" s="13">
-        <v>3</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="C4" s="4">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="D4" s="9">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E4" s="13">
-        <v>6.1428571428571432</v>
+        <v>5.2222222222222223</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>192</v>
+        <v>291</v>
       </c>
       <c r="C5" s="4">
-        <v>226</v>
+        <v>347</v>
       </c>
       <c r="D5" s="9">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="13">
-        <v>2.1428571428571428</v>
+        <v>1.8888888888888888</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>273</v>
+        <v>340</v>
       </c>
       <c r="C6" s="4">
-        <v>429</v>
+        <v>609</v>
       </c>
       <c r="D6" s="9">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E6" s="13">
-        <v>5.7142857142857144</v>
+        <v>4.7777777777777777</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="C7" s="4">
-        <v>360</v>
+        <v>525</v>
       </c>
       <c r="D7" s="9">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E7" s="13">
-        <v>7</v>
+        <v>6.1111111111111107</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>339</v>
+        <v>416</v>
       </c>
       <c r="C8" s="4">
-        <v>307</v>
+        <v>448</v>
       </c>
       <c r="D8" s="9">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E8" s="13">
-        <v>8.5714285714285712</v>
+        <v>7.1111111111111107</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>261</v>
+        <v>329</v>
       </c>
       <c r="C9" s="4">
-        <v>340</v>
+        <v>495</v>
       </c>
       <c r="D9" s="9">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="13">
-        <v>5</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C10" s="4">
-        <v>262</v>
+        <v>411</v>
       </c>
       <c r="D10" s="9">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E10" s="13">
-        <v>8</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="C11" s="4">
-        <v>225</v>
+        <v>408</v>
       </c>
       <c r="D11" s="9">
         <v>20</v>
       </c>
       <c r="E11" s="13">
-        <v>2.8571428571428572</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="C12" s="4">
-        <v>312</v>
+        <v>478</v>
       </c>
       <c r="D12" s="9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E12" s="13">
-        <v>4.1428571428571432</v>
+        <v>3.7777777777777777</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C13" s="4">
-        <v>330</v>
+        <v>422</v>
       </c>
       <c r="D13" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="13">
-        <v>3.4285714285714284</v>
+        <v>2.7777777777777777</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>237</v>
+        <v>290</v>
       </c>
       <c r="C14" s="4">
-        <v>290</v>
+        <v>446</v>
       </c>
       <c r="D14" s="9">
         <v>27</v>
       </c>
       <c r="E14" s="13">
-        <v>3.8571428571428572</v>
+        <v>3</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C15" s="4">
         <v>241</v>
       </c>
       <c r="D15" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="13">
-        <v>3.4285714285714284</v>
+        <v>2.7777777777777777</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C16" s="4">
-        <v>442</v>
+        <v>522</v>
       </c>
       <c r="D16" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="13">
-        <v>4.5714285714285712</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="C17" s="4">
-        <v>362</v>
+        <v>530</v>
       </c>
       <c r="D17" s="9">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E17" s="13">
-        <v>4.1428571428571432</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="C18" s="4">
-        <v>265</v>
+        <v>347</v>
       </c>
       <c r="D18" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E18" s="13">
-        <v>5.1428571428571432</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>4225</v>
+        <v>5065</v>
       </c>
       <c r="C19" s="6">
-        <v>5399</v>
+        <v>7559</v>
       </c>
       <c r="D19" s="10">
-        <v>578</v>
+        <v>631</v>
       </c>
       <c r="E19" s="14">
-        <v>4.8571428571428568</v>
+        <v>4.1241830065359482</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -984,9 +984,8 @@
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="31" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="31" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1122,8 +1121,12 @@
       <c r="K2" s="4">
         <v>108</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>97</v>
+      </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -1143,7 +1146,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>404</v>
+        <v>715</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1180,8 +1183,12 @@
       <c r="K3" s="4">
         <v>110</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="L3" s="4">
+        <v>116</v>
+      </c>
+      <c r="M3" s="4">
+        <v>107</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -1201,7 +1208,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>346</v>
+        <v>800</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1238,8 +1245,12 @@
       <c r="K4" s="4">
         <v>109</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="L4" s="4">
+        <v>112</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -1259,7 +1270,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>339</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1296,8 +1307,12 @@
       <c r="K5" s="4">
         <v>0</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="L5" s="4">
+        <v>119</v>
+      </c>
+      <c r="M5" s="4">
+        <v>101</v>
+      </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -1317,7 +1332,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>318</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1354,8 +1369,12 @@
       <c r="K6" s="4">
         <v>112</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="L6" s="4">
+        <v>129</v>
+      </c>
+      <c r="M6" s="4">
+        <v>118</v>
+      </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
@@ -1375,7 +1394,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>474</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1412,8 +1431,12 @@
       <c r="K7" s="4">
         <v>115</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="L7" s="4">
+        <v>115</v>
+      </c>
+      <c r="M7" s="4">
+        <v>115</v>
+      </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
@@ -1433,7 +1456,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>459</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1470,8 +1493,12 @@
       <c r="K8" s="4">
         <v>116</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="L8" s="4">
+        <v>101</v>
+      </c>
+      <c r="M8" s="4">
+        <v>117</v>
+      </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
@@ -1491,7 +1518,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>413</v>
+        <v>864</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1528,8 +1555,12 @@
       <c r="K9" s="4">
         <v>110</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="L9" s="4">
+        <v>123</v>
+      </c>
+      <c r="M9" s="4">
+        <v>100</v>
+      </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -1549,7 +1580,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>372</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1586,8 +1617,12 @@
       <c r="K10" s="4">
         <v>110</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
+      <c r="L10" s="4">
+        <v>117</v>
+      </c>
+      <c r="M10" s="4">
+        <v>106</v>
+      </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
@@ -1607,7 +1642,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>319</v>
+        <v>766</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1644,8 +1679,12 @@
       <c r="K11" s="4">
         <v>0</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+      <c r="L11" s="4">
+        <v>110</v>
+      </c>
+      <c r="M11" s="4">
+        <v>113</v>
+      </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
@@ -1665,7 +1704,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>222</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1702,8 +1741,12 @@
       <c r="K12" s="4">
         <v>110</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="L12" s="4">
+        <v>113</v>
+      </c>
+      <c r="M12" s="4">
+        <v>110</v>
+      </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
@@ -1723,7 +1766,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>340</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1760,8 +1803,12 @@
       <c r="K13" s="4">
         <v>103</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="L13" s="4">
+        <v>111</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
@@ -1781,7 +1828,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>297</v>
+        <v>623</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1818,8 +1865,12 @@
       <c r="K14" s="4">
         <v>114</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+      <c r="L14" s="4">
+        <v>102</v>
+      </c>
+      <c r="M14" s="4">
+        <v>107</v>
+      </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
@@ -1839,7 +1890,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>324</v>
+        <v>736</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1876,8 +1927,12 @@
       <c r="K15" s="4">
         <v>124</v>
       </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>11</v>
+      </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
@@ -1897,7 +1952,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>344</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -1934,8 +1989,12 @@
       <c r="K16" s="4">
         <v>102</v>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>103</v>
+      </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
@@ -1955,7 +2014,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>474</v>
+        <v>786</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -1992,8 +2051,12 @@
       <c r="K17" s="4">
         <v>113</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="L17" s="4">
+        <v>108</v>
+      </c>
+      <c r="M17" s="4">
+        <v>106</v>
+      </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
@@ -2013,7 +2076,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>393</v>
+        <v>839</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2050,8 +2113,12 @@
       <c r="K18" s="4">
         <v>103</v>
       </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
+      <c r="L18" s="4">
+        <v>113</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -2071,7 +2138,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>323</v>
+        <v>644</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2108,8 +2175,12 @@
       <c r="K19" s="6">
         <v>1659</v>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="L19" s="6">
+        <v>1589</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1411</v>
+      </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
@@ -2129,7 +2200,7 @@
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>6161</v>
+        <v>12624</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2202,7 +2273,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>4.8571428571428568</v>
+        <v>4.1241830065359482</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913A7486-A829-4FA4-AED4-684329DE30B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D81933-F91D-458E-80BC-DA859DBB5225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C2" s="4">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D2" s="9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" s="13">
-        <v>4.666666666666667</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -594,10 +594,10 @@
         <v>549</v>
       </c>
       <c r="D3" s="9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="13">
-        <v>2.3333333333333335</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="C4" s="4">
         <v>367</v>
       </c>
       <c r="D4" s="9">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="13">
-        <v>5.2222222222222223</v>
+        <v>4.5454545454545459</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C5" s="4">
         <v>347</v>
       </c>
       <c r="D5" s="9">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E5" s="13">
-        <v>1.8888888888888888</v>
+        <v>2.6363636363636362</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -651,10 +651,10 @@
         <v>609</v>
       </c>
       <c r="D6" s="9">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E6" s="13">
-        <v>4.7777777777777777</v>
+        <v>4.4545454545454541</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -670,10 +670,10 @@
         <v>525</v>
       </c>
       <c r="D7" s="9">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E7" s="13">
-        <v>6.1111111111111107</v>
+        <v>5.5454545454545459</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -689,10 +689,10 @@
         <v>448</v>
       </c>
       <c r="D8" s="9">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E8" s="13">
-        <v>7.1111111111111107</v>
+        <v>6.5454545454545459</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -708,10 +708,10 @@
         <v>495</v>
       </c>
       <c r="D9" s="9">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E9" s="13">
-        <v>4.2222222222222223</v>
+        <v>4.0909090909090908</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C10" s="4">
         <v>411</v>
       </c>
       <c r="D10" s="9">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E10" s="13">
-        <v>7.333333333333333</v>
+        <v>7.3636363636363633</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -746,10 +746,10 @@
         <v>408</v>
       </c>
       <c r="D11" s="9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E11" s="13">
-        <v>2.2222222222222223</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -765,10 +765,10 @@
         <v>478</v>
       </c>
       <c r="D12" s="9">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E12" s="13">
-        <v>3.7777777777777777</v>
+        <v>3.7272727272727271</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -784,10 +784,10 @@
         <v>422</v>
       </c>
       <c r="D13" s="9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E13" s="13">
-        <v>2.7777777777777777</v>
+        <v>2.8181818181818183</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -803,10 +803,10 @@
         <v>446</v>
       </c>
       <c r="D14" s="9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E14" s="13">
-        <v>3</v>
+        <v>2.7272727272727271</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="C15" s="4">
         <v>241</v>
       </c>
       <c r="D15" s="9">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E15" s="13">
-        <v>2.7777777777777777</v>
+        <v>2.7272727272727271</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -841,10 +841,10 @@
         <v>522</v>
       </c>
       <c r="D16" s="9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" s="13">
-        <v>3.6666666666666665</v>
+        <v>3.2727272727272729</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -860,10 +860,10 @@
         <v>530</v>
       </c>
       <c r="D17" s="9">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E17" s="13">
-        <v>4</v>
+        <v>3.5454545454545454</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="C18" s="4">
         <v>347</v>
       </c>
       <c r="D18" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" s="13">
-        <v>4.2222222222222223</v>
+        <v>3.5454545454545454</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>5065</v>
+        <v>5228</v>
       </c>
       <c r="C19" s="6">
-        <v>7559</v>
+        <v>7560</v>
       </c>
       <c r="D19" s="10">
-        <v>631</v>
+        <v>721</v>
       </c>
       <c r="E19" s="14">
-        <v>4.1241830065359482</v>
+        <v>3.855614973262032</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1127,8 +1127,12 @@
       <c r="M2" s="4">
         <v>97</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="N2" s="4">
+        <v>27</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -1146,7 +1150,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>715</v>
+        <v>742</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1189,8 +1193,12 @@
       <c r="M3" s="4">
         <v>107</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -1251,8 +1259,12 @@
       <c r="M4" s="4">
         <v>0</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>42</v>
+      </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -1270,7 +1282,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>660</v>
+        <v>702</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1313,8 +1325,12 @@
       <c r="M5" s="4">
         <v>101</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="N5" s="4">
+        <v>20</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
@@ -1332,7 +1348,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>638</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1375,8 +1391,12 @@
       <c r="M6" s="4">
         <v>118</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
@@ -1437,8 +1457,12 @@
       <c r="M7" s="4">
         <v>115</v>
       </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
@@ -1499,8 +1523,12 @@
       <c r="M8" s="4">
         <v>117</v>
       </c>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -1561,8 +1589,12 @@
       <c r="M9" s="4">
         <v>100</v>
       </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
@@ -1623,8 +1655,12 @@
       <c r="M10" s="4">
         <v>106</v>
       </c>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>13</v>
+      </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -1642,7 +1678,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>766</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1685,8 +1721,12 @@
       <c r="M11" s="4">
         <v>113</v>
       </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4">
+        <v>0</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -1747,8 +1787,12 @@
       <c r="M12" s="4">
         <v>110</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
@@ -1809,8 +1853,12 @@
       <c r="M13" s="4">
         <v>0</v>
       </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
@@ -1871,8 +1919,12 @@
       <c r="M14" s="4">
         <v>107</v>
       </c>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -1933,8 +1985,12 @@
       <c r="M15" s="4">
         <v>11</v>
       </c>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>35</v>
+      </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -1952,7 +2008,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>502</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -1995,8 +2051,12 @@
       <c r="M16" s="4">
         <v>103</v>
       </c>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -2057,8 +2117,12 @@
       <c r="M17" s="4">
         <v>106</v>
       </c>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -2119,8 +2183,12 @@
       <c r="M18" s="4">
         <v>0</v>
       </c>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
+      <c r="N18" s="4">
+        <v>27</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -2138,7 +2206,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>644</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2181,8 +2249,12 @@
       <c r="M19" s="6">
         <v>1411</v>
       </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
+      <c r="N19" s="6">
+        <v>74</v>
+      </c>
+      <c r="O19" s="6">
+        <v>90</v>
+      </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
@@ -2200,7 +2272,7 @@
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>12624</v>
+        <v>12788</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2273,7 +2345,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>4.1241830065359482</v>
+        <v>3.855614973262032</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D81933-F91D-458E-80BC-DA859DBB5225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8C219B-5F2B-4930-B104-3DB04458949D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="C2" s="4">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="D2" s="9">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E2" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="C3" s="4">
-        <v>549</v>
+        <v>632</v>
       </c>
       <c r="D3" s="9">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" s="13">
-        <v>2</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>335</v>
+        <v>417</v>
       </c>
       <c r="C4" s="4">
-        <v>367</v>
+        <v>501</v>
       </c>
       <c r="D4" s="9">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E4" s="13">
-        <v>4.5454545454545459</v>
+        <v>5.8181818181818183</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="C5" s="4">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="D5" s="9">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5" s="13">
-        <v>2.6363636363636362</v>
+        <v>2.9090909090909092</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="C6" s="4">
-        <v>609</v>
+        <v>700</v>
       </c>
       <c r="D6" s="9">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E6" s="13">
-        <v>4.4545454545454541</v>
+        <v>5.0909090909090908</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="C7" s="4">
-        <v>525</v>
+        <v>596</v>
       </c>
       <c r="D7" s="9">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E7" s="13">
-        <v>5.5454545454545459</v>
+        <v>6.3636363636363633</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>416</v>
+        <v>491</v>
       </c>
       <c r="C8" s="4">
-        <v>448</v>
+        <v>600</v>
       </c>
       <c r="D8" s="9">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E8" s="13">
-        <v>6.5454545454545459</v>
+        <v>7.1818181818181817</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>329</v>
+        <v>405</v>
       </c>
       <c r="C9" s="4">
-        <v>495</v>
+        <v>628</v>
       </c>
       <c r="D9" s="9">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E9" s="13">
-        <v>4.0909090909090908</v>
+        <v>5.2727272727272725</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>368</v>
+        <v>430</v>
       </c>
       <c r="C10" s="4">
-        <v>411</v>
+        <v>568</v>
       </c>
       <c r="D10" s="9">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E10" s="13">
-        <v>7.3636363636363633</v>
+        <v>8.454545454545455</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="C11" s="4">
-        <v>408</v>
+        <v>575</v>
       </c>
       <c r="D11" s="9">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E11" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="C12" s="4">
-        <v>478</v>
+        <v>555</v>
       </c>
       <c r="D12" s="9">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E12" s="13">
-        <v>3.7272727272727271</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>201</v>
+        <v>244</v>
       </c>
       <c r="C13" s="4">
-        <v>422</v>
+        <v>596</v>
       </c>
       <c r="D13" s="9">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E13" s="13">
-        <v>2.8181818181818183</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="C14" s="4">
-        <v>446</v>
+        <v>623</v>
       </c>
       <c r="D14" s="9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E14" s="13">
-        <v>2.7272727272727271</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="C15" s="4">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="D15" s="9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E15" s="13">
-        <v>2.7272727272727271</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="C16" s="4">
-        <v>522</v>
+        <v>694</v>
       </c>
       <c r="D16" s="9">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E16" s="13">
-        <v>3.2727272727272729</v>
+        <v>3.7272727272727271</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="C17" s="4">
-        <v>530</v>
+        <v>709</v>
       </c>
       <c r="D17" s="9">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E17" s="13">
-        <v>3.5454545454545454</v>
+        <v>3.8181818181818183</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>324</v>
+        <v>371</v>
       </c>
       <c r="C18" s="4">
-        <v>347</v>
+        <v>524</v>
       </c>
       <c r="D18" s="9">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E18" s="13">
-        <v>3.5454545454545454</v>
+        <v>4.4545454545454541</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>5228</v>
+        <v>6036</v>
       </c>
       <c r="C19" s="6">
-        <v>7560</v>
+        <v>9703</v>
       </c>
       <c r="D19" s="10">
-        <v>721</v>
+        <v>855</v>
       </c>
       <c r="E19" s="14">
-        <v>3.855614973262032</v>
+        <v>4.572192513368984</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1133,8 +1133,12 @@
       <c r="O2" s="4">
         <v>0</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>97</v>
+      </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
@@ -1199,8 +1203,12 @@
       <c r="O3" s="4">
         <v>0</v>
       </c>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="P3" s="4">
+        <v>112</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -1265,8 +1273,12 @@
       <c r="O4" s="4">
         <v>42</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="P4" s="4">
+        <v>110</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>106</v>
+      </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -1331,8 +1343,12 @@
       <c r="O5" s="4">
         <v>0</v>
       </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
+      <c r="P5" s="4">
+        <v>89</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
@@ -1397,8 +1413,12 @@
       <c r="O6" s="4">
         <v>0</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="P6" s="4">
+        <v>120</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -1463,8 +1483,12 @@
       <c r="O7" s="4">
         <v>0</v>
       </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>102</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -1529,8 +1553,12 @@
       <c r="O8" s="4">
         <v>0</v>
       </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="P8" s="4">
+        <v>115</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>112</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -1595,8 +1623,12 @@
       <c r="O9" s="4">
         <v>0</v>
       </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="P9" s="4">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>107</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -1661,8 +1693,12 @@
       <c r="O10" s="4">
         <v>13</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="P10" s="4">
+        <v>113</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>106</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -1727,8 +1763,12 @@
       <c r="O11" s="4">
         <v>0</v>
       </c>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+      <c r="P11" s="4">
+        <v>106</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>111</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -1793,8 +1833,12 @@
       <c r="O12" s="4">
         <v>0</v>
       </c>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+      <c r="P12" s="4">
+        <v>108</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -1859,8 +1903,12 @@
       <c r="O13" s="4">
         <v>0</v>
       </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
+      <c r="P13" s="4">
+        <v>105</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>112</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
@@ -1925,8 +1973,12 @@
       <c r="O14" s="4">
         <v>0</v>
       </c>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
+      <c r="P14" s="4">
+        <v>112</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>115</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
@@ -1991,8 +2043,12 @@
       <c r="O15" s="4">
         <v>35</v>
       </c>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
+      <c r="P15" s="4">
+        <v>121</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -2057,8 +2113,12 @@
       <c r="O16" s="4">
         <v>0</v>
       </c>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+      <c r="P16" s="4">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>106</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -2123,8 +2183,12 @@
       <c r="O17" s="4">
         <v>0</v>
       </c>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+      <c r="P17" s="4">
+        <v>114</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>110</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
@@ -2189,8 +2253,12 @@
       <c r="O18" s="4">
         <v>0</v>
       </c>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
+      <c r="P18" s="4">
+        <v>109</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>115</v>
+      </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
@@ -2255,8 +2323,12 @@
       <c r="O19" s="6">
         <v>90</v>
       </c>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
+      <c r="P19" s="6">
+        <v>1652</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>1299</v>
+      </c>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
@@ -2345,7 +2417,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.855614973262032</v>
+        <v>4.572192513368984</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8C219B-5F2B-4930-B104-3DB04458949D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F89E97-3605-4F68-B0BE-3DD026EA75E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="C2" s="4">
-        <v>480</v>
+        <v>536</v>
       </c>
       <c r="D2" s="9">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E2" s="13">
-        <v>5</v>
+        <v>4.8461538461538458</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>280</v>
+        <v>353</v>
       </c>
       <c r="C3" s="4">
-        <v>632</v>
+        <v>783</v>
       </c>
       <c r="D3" s="9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" s="13">
-        <v>2.2727272727272729</v>
+        <v>2.3846153846153846</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>417</v>
+        <v>506</v>
       </c>
       <c r="C4" s="4">
-        <v>501</v>
+        <v>627</v>
       </c>
       <c r="D4" s="9">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="E4" s="13">
-        <v>5.8181818181818183</v>
+        <v>5.9230769230769234</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="C5" s="4">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="D5" s="9">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E5" s="13">
-        <v>2.9090909090909092</v>
+        <v>3.0769230769230771</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>369</v>
+        <v>440</v>
       </c>
       <c r="C6" s="4">
-        <v>700</v>
+        <v>857</v>
       </c>
       <c r="D6" s="9">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E6" s="13">
-        <v>5.0909090909090908</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>435</v>
+        <v>501</v>
       </c>
       <c r="C7" s="4">
-        <v>596</v>
+        <v>739</v>
       </c>
       <c r="D7" s="9">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E7" s="13">
-        <v>6.3636363636363633</v>
+        <v>6.0769230769230766</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>491</v>
+        <v>556</v>
       </c>
       <c r="C8" s="4">
-        <v>600</v>
+        <v>728</v>
       </c>
       <c r="D8" s="9">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E8" s="13">
-        <v>7.1818181818181817</v>
+        <v>6.9230769230769234</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>405</v>
+        <v>479</v>
       </c>
       <c r="C9" s="4">
-        <v>628</v>
+        <v>765</v>
       </c>
       <c r="D9" s="9">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E9" s="13">
-        <v>5.2727272727272725</v>
+        <v>5.7692307692307692</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>430</v>
+        <v>516</v>
       </c>
       <c r="C10" s="4">
-        <v>568</v>
+        <v>702</v>
       </c>
       <c r="D10" s="9">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E10" s="13">
-        <v>8.454545454545455</v>
+        <v>8.3076923076923084</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="C11" s="4">
-        <v>575</v>
+        <v>695</v>
       </c>
       <c r="D11" s="9">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E11" s="13">
-        <v>3</v>
+        <v>3.2307692307692308</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>345</v>
+        <v>412</v>
       </c>
       <c r="C12" s="4">
-        <v>555</v>
+        <v>711</v>
       </c>
       <c r="D12" s="9">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E12" s="13">
-        <v>4</v>
+        <v>3.8461538461538463</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>244</v>
+        <v>293</v>
       </c>
       <c r="C13" s="4">
-        <v>596</v>
+        <v>726</v>
       </c>
       <c r="D13" s="9">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E13" s="13">
-        <v>3.4545454545454546</v>
+        <v>3.8461538461538463</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>340</v>
+        <v>405</v>
       </c>
       <c r="C14" s="4">
-        <v>623</v>
+        <v>762</v>
       </c>
       <c r="D14" s="9">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E14" s="13">
-        <v>3.4545454545454546</v>
+        <v>3.3846153846153846</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="C15" s="4">
-        <v>315</v>
+        <v>407</v>
       </c>
       <c r="D15" s="9">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E15" s="13">
-        <v>3.4545454545454546</v>
+        <v>3.3846153846153846</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="C16" s="4">
-        <v>694</v>
+        <v>844</v>
       </c>
       <c r="D16" s="9">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E16" s="13">
-        <v>3.7272727272727271</v>
+        <v>3.6153846153846154</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="C17" s="4">
-        <v>709</v>
+        <v>868</v>
       </c>
       <c r="D17" s="9">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E17" s="13">
-        <v>3.8181818181818183</v>
+        <v>3.5384615384615383</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="C18" s="4">
-        <v>524</v>
+        <v>671</v>
       </c>
       <c r="D18" s="9">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E18" s="13">
-        <v>4.4545454545454541</v>
+        <v>4.1538461538461542</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>6036</v>
+        <v>7075</v>
       </c>
       <c r="C19" s="6">
-        <v>9703</v>
+        <v>11856</v>
       </c>
       <c r="D19" s="10">
-        <v>855</v>
+        <v>1005</v>
       </c>
       <c r="E19" s="14">
-        <v>4.572192513368984</v>
+        <v>4.5475113122171944</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1139,8 +1139,12 @@
       <c r="Q2" s="4">
         <v>97</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>97</v>
+      </c>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
@@ -1154,7 +1158,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>742</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1209,8 +1213,12 @@
       <c r="Q3" s="4">
         <v>0</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
+      <c r="R3" s="4">
+        <v>116</v>
+      </c>
+      <c r="S3" s="4">
+        <v>108</v>
+      </c>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
@@ -1224,7 +1232,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>800</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1279,8 +1287,12 @@
       <c r="Q4" s="4">
         <v>106</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
+      <c r="R4" s="4">
+        <v>106</v>
+      </c>
+      <c r="S4" s="4">
+        <v>109</v>
+      </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
@@ -1294,7 +1306,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>702</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1344,13 +1356,17 @@
         <v>0</v>
       </c>
       <c r="P5" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q5" s="4">
         <v>0</v>
       </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <v>75</v>
+      </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
@@ -1364,7 +1380,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>658</v>
+        <v>823</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1419,8 +1435,12 @@
       <c r="Q6" s="4">
         <v>0</v>
       </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
+      <c r="R6" s="4">
+        <v>118</v>
+      </c>
+      <c r="S6" s="4">
+        <v>110</v>
+      </c>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
@@ -1434,7 +1454,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>949</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1489,8 +1509,12 @@
       <c r="Q7" s="4">
         <v>102</v>
       </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
+      <c r="R7" s="4">
+        <v>109</v>
+      </c>
+      <c r="S7" s="4">
+        <v>100</v>
+      </c>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
@@ -1504,7 +1528,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>929</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1559,8 +1583,12 @@
       <c r="Q8" s="4">
         <v>112</v>
       </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
+      <c r="R8" s="4">
+        <v>108</v>
+      </c>
+      <c r="S8" s="4">
+        <v>85</v>
+      </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
@@ -1574,7 +1602,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>864</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1629,8 +1657,12 @@
       <c r="Q9" s="4">
         <v>107</v>
       </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
+      <c r="R9" s="4">
+        <v>108</v>
+      </c>
+      <c r="S9" s="4">
+        <v>103</v>
+      </c>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
@@ -1644,7 +1676,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>824</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1699,8 +1731,12 @@
       <c r="Q10" s="4">
         <v>106</v>
       </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
+      <c r="R10" s="4">
+        <v>107</v>
+      </c>
+      <c r="S10" s="4">
+        <v>113</v>
+      </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
@@ -1714,7 +1750,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>779</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1769,8 +1805,12 @@
       <c r="Q11" s="4">
         <v>111</v>
       </c>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
+      <c r="R11" s="4">
+        <v>105</v>
+      </c>
+      <c r="S11" s="4">
+        <v>51</v>
+      </c>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
@@ -1784,7 +1824,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>557</v>
+        <v>930</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1839,8 +1879,12 @@
       <c r="Q12" s="4">
         <v>0</v>
       </c>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
+      <c r="R12" s="4">
+        <v>111</v>
+      </c>
+      <c r="S12" s="4">
+        <v>112</v>
+      </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
@@ -1854,7 +1898,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>792</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1909,8 +1953,12 @@
       <c r="Q13" s="4">
         <v>112</v>
       </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
+      <c r="R13" s="4">
+        <v>98</v>
+      </c>
+      <c r="S13" s="4">
+        <v>81</v>
+      </c>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
@@ -1924,7 +1972,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>623</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1979,8 +2027,12 @@
       <c r="Q14" s="4">
         <v>115</v>
       </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
+      <c r="R14" s="4">
+        <v>111</v>
+      </c>
+      <c r="S14" s="4">
+        <v>93</v>
+      </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
@@ -1994,7 +2046,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>736</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2049,8 +2101,12 @@
       <c r="Q15" s="4">
         <v>0</v>
       </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
+      <c r="R15" s="4">
+        <v>125</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
@@ -2064,7 +2120,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>537</v>
+        <v>783</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2119,8 +2175,12 @@
       <c r="Q16" s="4">
         <v>106</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
+      <c r="R16" s="4">
+        <v>101</v>
+      </c>
+      <c r="S16" s="4">
+        <v>107</v>
+      </c>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
@@ -2134,7 +2194,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>786</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2189,8 +2249,12 @@
       <c r="Q17" s="4">
         <v>110</v>
       </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
+      <c r="R17" s="4">
+        <v>110</v>
+      </c>
+      <c r="S17" s="4">
+        <v>96</v>
+      </c>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
@@ -2204,7 +2268,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>839</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2259,8 +2323,12 @@
       <c r="Q18" s="4">
         <v>115</v>
       </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
+      <c r="R18" s="4">
+        <v>109</v>
+      </c>
+      <c r="S18" s="4">
+        <v>109</v>
+      </c>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
@@ -2274,7 +2342,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>671</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2324,13 +2392,17 @@
         <v>90</v>
       </c>
       <c r="P19" s="6">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="Q19" s="6">
         <v>1299</v>
       </c>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
+      <c r="R19" s="6">
+        <v>1642</v>
+      </c>
+      <c r="S19" s="6">
+        <v>1549</v>
+      </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
@@ -2344,7 +2416,7 @@
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>12788</v>
+        <v>18931</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2417,7 +2489,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>4.572192513368984</v>
+        <v>4.5475113122171944</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F89E97-3605-4F68-B0BE-3DD026EA75E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40300C2-60EC-40B8-9786-8A64FEAAD176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>400</v>
+        <v>479</v>
       </c>
       <c r="C2" s="4">
-        <v>536</v>
+        <v>601</v>
       </c>
       <c r="D2" s="9">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E2" s="13">
-        <v>4.8461538461538458</v>
+        <v>5.1428571428571432</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="C3" s="4">
-        <v>783</v>
+        <v>861</v>
       </c>
       <c r="D3" s="9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E3" s="13">
-        <v>2.3846153846153846</v>
+        <v>2.7857142857142856</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>506</v>
+        <v>577</v>
       </c>
       <c r="C4" s="4">
-        <v>627</v>
+        <v>693</v>
       </c>
       <c r="D4" s="9">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E4" s="13">
-        <v>5.9230769230769234</v>
+        <v>6.3571428571428568</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>388</v>
+        <v>468</v>
       </c>
       <c r="C5" s="4">
-        <v>435</v>
+        <v>481</v>
       </c>
       <c r="D5" s="9">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E5" s="13">
-        <v>3.0769230769230771</v>
+        <v>4.4285714285714288</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>440</v>
+        <v>485</v>
       </c>
       <c r="C6" s="4">
-        <v>857</v>
+        <v>936</v>
       </c>
       <c r="D6" s="9">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E6" s="13">
-        <v>5</v>
+        <v>5.2142857142857144</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>501</v>
+        <v>541</v>
       </c>
       <c r="C7" s="4">
-        <v>739</v>
+        <v>813</v>
       </c>
       <c r="D7" s="9">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E7" s="13">
-        <v>6.0769230769230766</v>
+        <v>6.1428571428571432</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>556</v>
+        <v>605</v>
       </c>
       <c r="C8" s="4">
-        <v>728</v>
+        <v>796</v>
       </c>
       <c r="D8" s="9">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E8" s="13">
-        <v>6.9230769230769234</v>
+        <v>7.5</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="C9" s="4">
-        <v>765</v>
+        <v>837</v>
       </c>
       <c r="D9" s="9">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E9" s="13">
-        <v>5.7692307692307692</v>
+        <v>6.2142857142857144</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="C10" s="4">
         <v>702</v>
       </c>
       <c r="D10" s="9">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E10" s="13">
-        <v>8.3076923076923084</v>
+        <v>8.2142857142857135</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C11" s="4">
-        <v>695</v>
+        <v>777</v>
       </c>
       <c r="D11" s="9">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E11" s="13">
-        <v>3.2307692307692308</v>
+        <v>3.2142857142857144</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -765,10 +765,10 @@
         <v>711</v>
       </c>
       <c r="D12" s="9">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E12" s="13">
-        <v>3.8461538461538463</v>
+        <v>3.8571428571428572</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C13" s="4">
-        <v>726</v>
+        <v>784</v>
       </c>
       <c r="D13" s="9">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E13" s="13">
-        <v>3.8461538461538463</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="C14" s="4">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="D14" s="9">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E14" s="13">
-        <v>3.3846153846153846</v>
+        <v>3.5</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="C15" s="4">
         <v>407</v>
       </c>
       <c r="D15" s="9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="13">
-        <v>3.3846153846153846</v>
+        <v>3.2142857142857144</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="C16" s="4">
-        <v>844</v>
+        <v>919</v>
       </c>
       <c r="D16" s="9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E16" s="13">
-        <v>3.6153846153846154</v>
+        <v>3.6428571428571428</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="C17" s="4">
-        <v>868</v>
+        <v>945</v>
       </c>
       <c r="D17" s="9">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E17" s="13">
-        <v>3.5384615384615383</v>
+        <v>3.6428571428571428</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="C18" s="4">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D18" s="9">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E18" s="13">
-        <v>4.1538461538461542</v>
+        <v>4.5714285714285712</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>7075</v>
+        <v>7740</v>
       </c>
       <c r="C19" s="6">
-        <v>11856</v>
+        <v>12755</v>
       </c>
       <c r="D19" s="10">
-        <v>1005</v>
+        <v>1143</v>
       </c>
       <c r="E19" s="14">
-        <v>4.5475113122171944</v>
+        <v>4.8025210084033612</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1145,9 +1145,15 @@
       <c r="S2" s="4">
         <v>97</v>
       </c>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="T2" s="4">
+        <v>105</v>
+      </c>
+      <c r="U2" s="4">
+        <v>39</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
@@ -1158,7 +1164,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>936</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1219,9 +1225,15 @@
       <c r="S3" s="4">
         <v>108</v>
       </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="T3" s="4">
+        <v>118</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
@@ -1232,7 +1244,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1136</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1293,9 +1305,15 @@
       <c r="S4" s="4">
         <v>109</v>
       </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+      <c r="T4" s="4">
+        <v>113</v>
+      </c>
+      <c r="U4" s="4">
+        <v>24</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1306,7 +1324,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1133</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1367,9 +1385,15 @@
       <c r="S5" s="4">
         <v>75</v>
       </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+      <c r="T5" s="4">
+        <v>102</v>
+      </c>
+      <c r="U5" s="4">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <v>24</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1380,7 +1404,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>823</v>
+        <v>949</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1441,9 +1465,15 @@
       <c r="S6" s="4">
         <v>110</v>
       </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
+      <c r="T6" s="4">
+        <v>124</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
@@ -1454,7 +1484,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1297</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1515,9 +1545,15 @@
       <c r="S7" s="4">
         <v>100</v>
       </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="T7" s="4">
+        <v>114</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -1528,7 +1564,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1240</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1589,9 +1625,15 @@
       <c r="S8" s="4">
         <v>85</v>
       </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
+      <c r="T8" s="4">
+        <v>117</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -1602,7 +1644,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1284</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1663,9 +1705,15 @@
       <c r="S9" s="4">
         <v>103</v>
       </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
+      <c r="T9" s="4">
+        <v>109</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4">
+        <v>0</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -1676,7 +1724,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1244</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1737,9 +1785,15 @@
       <c r="S10" s="4">
         <v>113</v>
       </c>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <v>24</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1750,7 +1804,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1218</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1811,9 +1865,15 @@
       <c r="S11" s="4">
         <v>51</v>
       </c>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
+      <c r="T11" s="4">
+        <v>104</v>
+      </c>
+      <c r="U11" s="4">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4">
+        <v>0</v>
+      </c>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1824,7 +1884,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>930</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1885,9 +1945,15 @@
       <c r="S12" s="4">
         <v>112</v>
       </c>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+      <c r="T12" s="4">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
+        <v>0</v>
+      </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1959,9 +2025,15 @@
       <c r="S13" s="4">
         <v>81</v>
       </c>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
+      <c r="T13" s="4">
+        <v>80</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
+        <v>0</v>
+      </c>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
@@ -1972,7 +2044,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1019</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2033,9 +2105,15 @@
       <c r="S14" s="4">
         <v>93</v>
       </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
+      <c r="T14" s="4">
+        <v>86</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
+        <v>0</v>
+      </c>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
@@ -2046,7 +2124,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>1167</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2107,9 +2185,15 @@
       <c r="S15" s="4">
         <v>0</v>
       </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>45</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -2120,7 +2204,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>783</v>
+        <v>828</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2181,9 +2265,15 @@
       <c r="S16" s="4">
         <v>107</v>
       </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
+      <c r="T16" s="4">
+        <v>110</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2194,7 +2284,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1216</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2255,9 +2345,15 @@
       <c r="S17" s="4">
         <v>96</v>
       </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
+      <c r="T17" s="4">
+        <v>106</v>
+      </c>
+      <c r="U17" s="4">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
+        <v>0</v>
+      </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -2268,7 +2364,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1269</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2329,9 +2425,15 @@
       <c r="S18" s="4">
         <v>109</v>
       </c>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
+      <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
+        <v>20</v>
+      </c>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -2342,7 +2444,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>1113</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2403,9 +2505,15 @@
       <c r="S19" s="6">
         <v>1549</v>
       </c>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
+      <c r="T19" s="6">
+        <v>1388</v>
+      </c>
+      <c r="U19" s="6">
+        <v>108</v>
+      </c>
+      <c r="V19" s="6">
+        <v>68</v>
+      </c>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
@@ -2416,7 +2524,7 @@
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>18931</v>
+        <v>20495</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2489,7 +2597,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>4.5475113122171944</v>
+        <v>4.8025210084033612</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40300C2-60EC-40B8-9786-8A64FEAAD176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDC7887-A4BA-4F27-AD67-61109473B7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -708,10 +708,10 @@
         <v>837</v>
       </c>
       <c r="D9" s="9">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="13">
-        <v>6.2142857142857144</v>
+        <v>6.2857142857142856</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -765,10 +765,10 @@
         <v>711</v>
       </c>
       <c r="D12" s="9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="13">
-        <v>3.8571428571428572</v>
+        <v>3.7857142857142856</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDC7887-A4BA-4F27-AD67-61109473B7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5375BE11-7BD1-4B27-A1BD-EC1A4B7A2A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>479</v>
+        <v>562</v>
       </c>
       <c r="C2" s="4">
-        <v>601</v>
+        <v>728</v>
       </c>
       <c r="D2" s="9">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E2" s="13">
-        <v>5.1428571428571432</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>393</v>
+        <v>476</v>
       </c>
       <c r="C3" s="4">
-        <v>861</v>
+        <v>1002</v>
       </c>
       <c r="D3" s="9">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E3" s="13">
-        <v>2.7857142857142856</v>
+        <v>2.8125</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>577</v>
+        <v>658</v>
       </c>
       <c r="C4" s="4">
-        <v>693</v>
+        <v>735</v>
       </c>
       <c r="D4" s="9">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E4" s="13">
-        <v>6.3571428571428568</v>
+        <v>6.5625</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>468</v>
+        <v>519</v>
       </c>
       <c r="C5" s="4">
-        <v>481</v>
+        <v>531</v>
       </c>
       <c r="D5" s="9">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E5" s="13">
-        <v>4.4285714285714288</v>
+        <v>4.3125</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>485</v>
+        <v>529</v>
       </c>
       <c r="C6" s="4">
-        <v>936</v>
+        <v>1003</v>
       </c>
       <c r="D6" s="9">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E6" s="13">
-        <v>5.2142857142857144</v>
+        <v>5.125</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>541</v>
+        <v>635</v>
       </c>
       <c r="C7" s="4">
-        <v>813</v>
+        <v>948</v>
       </c>
       <c r="D7" s="9">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="E7" s="13">
-        <v>6.1428571428571432</v>
+        <v>6.3125</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>605</v>
+        <v>713</v>
       </c>
       <c r="C8" s="4">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="D8" s="9">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="E8" s="13">
-        <v>7.5</v>
+        <v>7.9375</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>516</v>
+        <v>594</v>
       </c>
       <c r="C9" s="4">
-        <v>837</v>
+        <v>963</v>
       </c>
       <c r="D9" s="9">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E9" s="13">
-        <v>6.2857142857142856</v>
+        <v>6.125</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>540</v>
+        <v>632</v>
       </c>
       <c r="C10" s="4">
-        <v>702</v>
+        <v>823</v>
       </c>
       <c r="D10" s="9">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="E10" s="13">
-        <v>8.2142857142857135</v>
+        <v>8.25</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="C11" s="4">
-        <v>777</v>
+        <v>934</v>
       </c>
       <c r="D11" s="9">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E11" s="13">
-        <v>3.2142857142857144</v>
+        <v>3.0625</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C12" s="4">
-        <v>711</v>
+        <v>791</v>
       </c>
       <c r="D12" s="9">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E12" s="13">
-        <v>3.7857142857142856</v>
+        <v>3.625</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="C13" s="4">
-        <v>784</v>
+        <v>934</v>
       </c>
       <c r="D13" s="9">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E13" s="13">
-        <v>4</v>
+        <v>4.1875</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>433</v>
+        <v>520</v>
       </c>
       <c r="C14" s="4">
-        <v>820</v>
+        <v>934</v>
       </c>
       <c r="D14" s="9">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E14" s="13">
-        <v>3.5</v>
+        <v>3.625</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>421</v>
+        <v>493</v>
       </c>
       <c r="C15" s="4">
-        <v>407</v>
+        <v>603</v>
       </c>
       <c r="D15" s="9">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E15" s="13">
-        <v>3.2142857142857144</v>
+        <v>3.5625</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>407</v>
+        <v>469</v>
       </c>
       <c r="C16" s="4">
-        <v>919</v>
+        <v>1068</v>
       </c>
       <c r="D16" s="9">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E16" s="13">
-        <v>3.6428571428571428</v>
+        <v>3.625</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>430</v>
+        <v>488</v>
       </c>
       <c r="C17" s="4">
-        <v>945</v>
+        <v>1103</v>
       </c>
       <c r="D17" s="9">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E17" s="13">
-        <v>3.6428571428571428</v>
+        <v>3.5625</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="C18" s="4">
-        <v>672</v>
+        <v>738</v>
       </c>
       <c r="D18" s="9">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E18" s="13">
-        <v>4.5714285714285712</v>
+        <v>4.625</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>7740</v>
+        <v>8910</v>
       </c>
       <c r="C19" s="6">
-        <v>12755</v>
+        <v>14771</v>
       </c>
       <c r="D19" s="10">
-        <v>1143</v>
+        <v>1317</v>
       </c>
       <c r="E19" s="14">
-        <v>4.8025210084033612</v>
+        <v>4.8419117647058822</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1154,8 +1154,12 @@
       <c r="V2" s="4">
         <v>0</v>
       </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="W2" s="4">
+        <v>104</v>
+      </c>
+      <c r="X2" s="4">
+        <v>106</v>
+      </c>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
@@ -1164,7 +1168,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1080</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1234,8 +1238,12 @@
       <c r="V3" s="4">
         <v>0</v>
       </c>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
+      <c r="W3" s="4">
+        <v>112</v>
+      </c>
+      <c r="X3" s="4">
+        <v>112</v>
+      </c>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -1244,7 +1252,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1254</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1314,8 +1322,12 @@
       <c r="V4" s="4">
         <v>0</v>
       </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
+      <c r="W4" s="4">
+        <v>6</v>
+      </c>
+      <c r="X4" s="4">
+        <v>117</v>
+      </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -1324,7 +1336,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1270</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1394,8 +1406,12 @@
       <c r="V5" s="4">
         <v>24</v>
       </c>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
+      <c r="W5" s="4">
+        <v>101</v>
+      </c>
+      <c r="X5" s="4">
+        <v>0</v>
+      </c>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -1404,7 +1420,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>949</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1474,8 +1490,12 @@
       <c r="V6" s="4">
         <v>0</v>
       </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
+      <c r="W6" s="4">
+        <v>111</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -1484,7 +1504,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1421</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1554,8 +1574,12 @@
       <c r="V7" s="4">
         <v>0</v>
       </c>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
+      <c r="W7" s="4">
+        <v>113</v>
+      </c>
+      <c r="X7" s="4">
+        <v>116</v>
+      </c>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
@@ -1564,7 +1588,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1354</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1634,8 +1658,12 @@
       <c r="V8" s="4">
         <v>0</v>
       </c>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
+      <c r="W8" s="4">
+        <v>121</v>
+      </c>
+      <c r="X8" s="4">
+        <v>124</v>
+      </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
@@ -1644,7 +1672,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1401</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1714,8 +1742,12 @@
       <c r="V9" s="4">
         <v>0</v>
       </c>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
+      <c r="W9" s="4">
+        <v>102</v>
+      </c>
+      <c r="X9" s="4">
+        <v>102</v>
+      </c>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -1724,7 +1756,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1353</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1794,8 +1826,12 @@
       <c r="V10" s="4">
         <v>24</v>
       </c>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
+      <c r="W10" s="4">
+        <v>104</v>
+      </c>
+      <c r="X10" s="4">
+        <v>109</v>
+      </c>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
@@ -1804,7 +1840,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1242</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1874,8 +1910,12 @@
       <c r="V11" s="4">
         <v>0</v>
       </c>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
+      <c r="W11" s="4">
+        <v>107</v>
+      </c>
+      <c r="X11" s="4">
+        <v>104</v>
+      </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -1884,7 +1924,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1034</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1954,8 +1994,12 @@
       <c r="V12" s="4">
         <v>0</v>
       </c>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
+      <c r="W12" s="4">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4">
+        <v>104</v>
+      </c>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -1964,7 +2008,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>1123</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2034,8 +2078,12 @@
       <c r="V13" s="4">
         <v>0</v>
       </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
+      <c r="W13" s="4">
+        <v>110</v>
+      </c>
+      <c r="X13" s="4">
+        <v>101</v>
+      </c>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
@@ -2044,7 +2092,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1099</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2114,8 +2162,12 @@
       <c r="V14" s="4">
         <v>0</v>
       </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
+      <c r="W14" s="4">
+        <v>108</v>
+      </c>
+      <c r="X14" s="4">
+        <v>93</v>
+      </c>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
@@ -2124,7 +2176,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>1253</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2194,8 +2246,12 @@
       <c r="V15" s="4">
         <v>0</v>
       </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
+      <c r="W15" s="4">
+        <v>143</v>
+      </c>
+      <c r="X15" s="4">
+        <v>125</v>
+      </c>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
@@ -2204,7 +2260,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>828</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2274,8 +2330,12 @@
       <c r="V16" s="4">
         <v>0</v>
       </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="W16" s="4">
+        <v>107</v>
+      </c>
+      <c r="X16" s="4">
+        <v>104</v>
+      </c>
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
@@ -2284,7 +2344,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1326</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2354,8 +2414,12 @@
       <c r="V17" s="4">
         <v>0</v>
       </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+      <c r="W17" s="4">
+        <v>109</v>
+      </c>
+      <c r="X17" s="4">
+        <v>107</v>
+      </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -2364,7 +2428,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1375</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2434,8 +2498,12 @@
       <c r="V18" s="4">
         <v>20</v>
       </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
+      <c r="W18" s="4">
+        <v>0</v>
+      </c>
+      <c r="X18" s="4">
+        <v>104</v>
+      </c>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
@@ -2444,7 +2512,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>1133</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2514,8 +2582,12 @@
       <c r="V19" s="6">
         <v>68</v>
       </c>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
+      <c r="W19" s="6">
+        <v>1558</v>
+      </c>
+      <c r="X19" s="6">
+        <v>1628</v>
+      </c>
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
@@ -2524,7 +2596,7 @@
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>20495</v>
+        <v>23681</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2597,7 +2669,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>4.8025210084033612</v>
+        <v>4.8419117647058822</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5375BE11-7BD1-4B27-A1BD-EC1A4B7A2A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FD9ADE-4F09-4EC0-9774-D2CE6BA5974A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>562</v>
+        <v>596</v>
       </c>
       <c r="C2" s="4">
-        <v>728</v>
+        <v>811</v>
       </c>
       <c r="D2" s="9">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E2" s="13">
-        <v>5</v>
+        <v>4.8888888888888893</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>476</v>
+        <v>554</v>
       </c>
       <c r="C3" s="4">
-        <v>1002</v>
+        <v>1180</v>
       </c>
       <c r="D3" s="9">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E3" s="13">
-        <v>2.8125</v>
+        <v>3.2222222222222223</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>658</v>
+        <v>755</v>
       </c>
       <c r="C4" s="4">
-        <v>735</v>
+        <v>918</v>
       </c>
       <c r="D4" s="9">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E4" s="13">
-        <v>6.5625</v>
+        <v>7.1111111111111107</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>519</v>
+        <v>618</v>
       </c>
       <c r="C5" s="4">
-        <v>531</v>
+        <v>735</v>
       </c>
       <c r="D5" s="9">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E5" s="13">
-        <v>4.3125</v>
+        <v>4.3888888888888893</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>529</v>
+        <v>601</v>
       </c>
       <c r="C6" s="4">
-        <v>1003</v>
+        <v>1177</v>
       </c>
       <c r="D6" s="9">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E6" s="13">
-        <v>5.125</v>
+        <v>5.0555555555555554</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>635</v>
+        <v>709</v>
       </c>
       <c r="C7" s="4">
-        <v>948</v>
+        <v>1119</v>
       </c>
       <c r="D7" s="9">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E7" s="13">
-        <v>6.3125</v>
+        <v>6.2777777777777777</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>713</v>
+        <v>805</v>
       </c>
       <c r="C8" s="4">
-        <v>933</v>
+        <v>1150</v>
       </c>
       <c r="D8" s="9">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="E8" s="13">
-        <v>7.9375</v>
+        <v>8.2222222222222214</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>594</v>
+        <v>666</v>
       </c>
       <c r="C9" s="4">
-        <v>963</v>
+        <v>1111</v>
       </c>
       <c r="D9" s="9">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E9" s="13">
-        <v>6.125</v>
+        <v>6.5555555555555554</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>632</v>
+        <v>729</v>
       </c>
       <c r="C10" s="4">
-        <v>823</v>
+        <v>971</v>
       </c>
       <c r="D10" s="9">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="E10" s="13">
-        <v>8.25</v>
+        <v>8.2777777777777786</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C11" s="4">
-        <v>934</v>
+        <v>1026</v>
       </c>
       <c r="D11" s="9">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E11" s="13">
-        <v>3.0625</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>436</v>
+        <v>510</v>
       </c>
       <c r="C12" s="4">
-        <v>791</v>
+        <v>970</v>
       </c>
       <c r="D12" s="9">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E12" s="13">
-        <v>3.625</v>
+        <v>3.7222222222222223</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="C13" s="4">
-        <v>934</v>
+        <v>1140</v>
       </c>
       <c r="D13" s="9">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E13" s="13">
-        <v>4.1875</v>
+        <v>4.4444444444444446</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>520</v>
+        <v>591</v>
       </c>
       <c r="C14" s="4">
-        <v>934</v>
+        <v>1099</v>
       </c>
       <c r="D14" s="9">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E14" s="13">
-        <v>3.625</v>
+        <v>3.6111111111111112</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="C15" s="4">
-        <v>603</v>
+        <v>683</v>
       </c>
       <c r="D15" s="9">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E15" s="13">
-        <v>3.5625</v>
+        <v>3.5555555555555554</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>469</v>
+        <v>524</v>
       </c>
       <c r="C16" s="4">
-        <v>1068</v>
+        <v>1236</v>
       </c>
       <c r="D16" s="9">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E16" s="13">
-        <v>3.625</v>
+        <v>3.7777777777777777</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>488</v>
+        <v>557</v>
       </c>
       <c r="C17" s="4">
-        <v>1103</v>
+        <v>1255</v>
       </c>
       <c r="D17" s="9">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E17" s="13">
-        <v>3.5625</v>
+        <v>3.7777777777777777</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="C18" s="4">
-        <v>738</v>
+        <v>810</v>
       </c>
       <c r="D18" s="9">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E18" s="13">
-        <v>4.625</v>
+        <v>4.6111111111111107</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>8910</v>
+        <v>10050</v>
       </c>
       <c r="C19" s="6">
-        <v>14771</v>
+        <v>17391</v>
       </c>
       <c r="D19" s="10">
-        <v>1317</v>
+        <v>1521</v>
       </c>
       <c r="E19" s="14">
-        <v>4.8419117647058822</v>
+        <v>4.9705882352941178</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1160,15 +1160,19 @@
       <c r="X2" s="4">
         <v>106</v>
       </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>117</v>
+      </c>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1290</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1244,15 +1248,19 @@
       <c r="X3" s="4">
         <v>112</v>
       </c>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
+      <c r="Y3" s="4">
+        <v>114</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>142</v>
+      </c>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1478</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1328,15 +1336,19 @@
       <c r="X4" s="4">
         <v>117</v>
       </c>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
+      <c r="Y4" s="4">
+        <v>116</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>164</v>
+      </c>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1393</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1412,15 +1424,19 @@
       <c r="X5" s="4">
         <v>0</v>
       </c>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
+      <c r="Y5" s="4">
+        <v>105</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>198</v>
+      </c>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>1050</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1496,15 +1512,19 @@
       <c r="X6" s="4">
         <v>0</v>
       </c>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
+      <c r="Y6" s="4">
+        <v>116</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>130</v>
+      </c>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1532</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1580,15 +1600,19 @@
       <c r="X7" s="4">
         <v>116</v>
       </c>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
+      <c r="Y7" s="4">
+        <v>104</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>141</v>
+      </c>
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1583</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1664,15 +1688,19 @@
       <c r="X8" s="4">
         <v>124</v>
       </c>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
+      <c r="Y8" s="4">
+        <v>127</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>182</v>
+      </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1646</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1748,15 +1776,19 @@
       <c r="X9" s="4">
         <v>102</v>
       </c>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
+      <c r="Y9" s="4">
+        <v>106</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>114</v>
+      </c>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1557</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1832,15 +1864,19 @@
       <c r="X10" s="4">
         <v>109</v>
       </c>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
+      <c r="Y10" s="4">
+        <v>107</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>138</v>
+      </c>
       <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1455</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1916,15 +1952,19 @@
       <c r="X11" s="4">
         <v>104</v>
       </c>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
+      <c r="Y11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>118</v>
+      </c>
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1245</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2000,15 +2040,19 @@
       <c r="X12" s="4">
         <v>104</v>
       </c>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
+      <c r="Y12" s="4">
+        <v>121</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>132</v>
+      </c>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>1227</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2084,15 +2128,19 @@
       <c r="X13" s="4">
         <v>101</v>
       </c>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
+      <c r="Y13" s="4">
+        <v>107</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>156</v>
+      </c>
       <c r="AA13" s="4"/>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1310</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2168,15 +2216,19 @@
       <c r="X14" s="4">
         <v>93</v>
       </c>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
+      <c r="Y14" s="4">
+        <v>102</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>134</v>
+      </c>
       <c r="AA14" s="4"/>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>1454</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2252,15 +2304,19 @@
       <c r="X15" s="4">
         <v>125</v>
       </c>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
+      <c r="Y15" s="4">
+        <v>119</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>1096</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2336,15 +2392,19 @@
       <c r="X16" s="4">
         <v>104</v>
       </c>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
+      <c r="Y16" s="4">
+        <v>106</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>117</v>
+      </c>
       <c r="AA16" s="4"/>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1537</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2420,15 +2480,19 @@
       <c r="X17" s="4">
         <v>107</v>
       </c>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
+      <c r="Y17" s="4">
+        <v>105</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>116</v>
+      </c>
       <c r="AA17" s="4"/>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1591</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2504,15 +2568,19 @@
       <c r="X18" s="4">
         <v>104</v>
       </c>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
+      <c r="Y18" s="4">
+        <v>106</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>0</v>
+      </c>
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>1237</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2588,15 +2656,19 @@
       <c r="X19" s="6">
         <v>1628</v>
       </c>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
+      <c r="Y19" s="6">
+        <v>1661</v>
+      </c>
+      <c r="Z19" s="6">
+        <v>2099</v>
+      </c>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6"/>
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>23681</v>
+        <v>27441</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2669,7 +2741,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>4.8419117647058822</v>
+        <v>4.9705882352941178</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FD9ADE-4F09-4EC0-9774-D2CE6BA5974A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F851B7F-7D87-4A8B-8BD2-59CB8D8E75A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>596</v>
+        <v>704</v>
       </c>
       <c r="C2" s="4">
-        <v>811</v>
+        <v>949</v>
       </c>
       <c r="D2" s="9">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E2" s="13">
-        <v>4.8888888888888893</v>
+        <v>5.6</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>554</v>
+        <v>639</v>
       </c>
       <c r="C3" s="4">
-        <v>1180</v>
+        <v>1334</v>
       </c>
       <c r="D3" s="9">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E3" s="13">
-        <v>3.2222222222222223</v>
+        <v>3.65</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -607,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>755</v>
+        <v>849</v>
       </c>
       <c r="C4" s="4">
-        <v>918</v>
+        <v>1076</v>
       </c>
       <c r="D4" s="9">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E4" s="13">
-        <v>7.1111111111111107</v>
+        <v>7.25</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>618</v>
+        <v>716</v>
       </c>
       <c r="C5" s="4">
-        <v>735</v>
+        <v>894</v>
       </c>
       <c r="D5" s="9">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E5" s="13">
-        <v>4.3888888888888893</v>
+        <v>5.05</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>601</v>
+        <v>664</v>
       </c>
       <c r="C6" s="4">
-        <v>1177</v>
+        <v>1341</v>
       </c>
       <c r="D6" s="9">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E6" s="13">
-        <v>5.0555555555555554</v>
+        <v>5.4</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>709</v>
+        <v>778</v>
       </c>
       <c r="C7" s="4">
-        <v>1119</v>
+        <v>1266</v>
       </c>
       <c r="D7" s="9">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E7" s="13">
-        <v>6.2777777777777777</v>
+        <v>6.55</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>805</v>
+        <v>882</v>
       </c>
       <c r="C8" s="4">
-        <v>1150</v>
+        <v>1320</v>
       </c>
       <c r="D8" s="9">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E8" s="13">
-        <v>8.2222222222222214</v>
+        <v>7.95</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>666</v>
+        <v>730</v>
       </c>
       <c r="C9" s="4">
-        <v>1111</v>
+        <v>1277</v>
       </c>
       <c r="D9" s="9">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="E9" s="13">
-        <v>6.5555555555555554</v>
+        <v>7.35</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>729</v>
+        <v>819</v>
       </c>
       <c r="C10" s="4">
-        <v>971</v>
+        <v>1051</v>
       </c>
       <c r="D10" s="9">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E10" s="13">
-        <v>8.2777777777777786</v>
+        <v>8.25</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="C11" s="4">
-        <v>1026</v>
+        <v>1243</v>
       </c>
       <c r="D11" s="9">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E11" s="13">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>510</v>
+        <v>586</v>
       </c>
       <c r="C12" s="4">
-        <v>970</v>
+        <v>1133</v>
       </c>
       <c r="D12" s="9">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E12" s="13">
-        <v>3.7222222222222223</v>
+        <v>3.95</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="C13" s="4">
-        <v>1140</v>
+        <v>1212</v>
       </c>
       <c r="D13" s="9">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E13" s="13">
-        <v>4.4444444444444446</v>
+        <v>4.45</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -803,10 +803,10 @@
         <v>1099</v>
       </c>
       <c r="D14" s="9">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E14" s="13">
-        <v>3.6111111111111112</v>
+        <v>3.8</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -816,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>532</v>
+        <v>566</v>
       </c>
       <c r="C15" s="4">
         <v>683</v>
       </c>
       <c r="D15" s="9">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E15" s="13">
-        <v>3.5555555555555554</v>
+        <v>3.45</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="C16" s="4">
-        <v>1236</v>
+        <v>1393</v>
       </c>
       <c r="D16" s="9">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E16" s="13">
-        <v>3.7777777777777777</v>
+        <v>4.05</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>557</v>
+        <v>620</v>
       </c>
       <c r="C17" s="4">
-        <v>1255</v>
+        <v>1410</v>
       </c>
       <c r="D17" s="9">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E17" s="13">
-        <v>3.7777777777777777</v>
+        <v>4.05</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>533</v>
+        <v>627</v>
       </c>
       <c r="C18" s="4">
-        <v>810</v>
+        <v>959</v>
       </c>
       <c r="D18" s="9">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E18" s="13">
-        <v>4.6111111111111107</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>10050</v>
+        <v>11236</v>
       </c>
       <c r="C19" s="6">
-        <v>17391</v>
+        <v>19640</v>
       </c>
       <c r="D19" s="10">
-        <v>1521</v>
+        <v>1780</v>
       </c>
       <c r="E19" s="14">
-        <v>4.9705882352941178</v>
+        <v>5.2352941176470589</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1166,13 +1166,21 @@
       <c r="Z2" s="4">
         <v>117</v>
       </c>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
+      <c r="AA2" s="4">
+        <v>104</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>32</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>110</v>
+      </c>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1407</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1254,13 +1262,21 @@
       <c r="Z3" s="4">
         <v>142</v>
       </c>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
+      <c r="AA3" s="4">
+        <v>124</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>115</v>
+      </c>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1734</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1342,13 +1358,21 @@
       <c r="Z4" s="4">
         <v>164</v>
       </c>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
+      <c r="AA4" s="4">
+        <v>120</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>33</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>99</v>
+      </c>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1673</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1430,13 +1454,21 @@
       <c r="Z5" s="4">
         <v>198</v>
       </c>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
+      <c r="AA5" s="4">
+        <v>114</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>44</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>99</v>
+      </c>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>1353</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1518,13 +1550,21 @@
       <c r="Z6" s="4">
         <v>130</v>
       </c>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
+      <c r="AA6" s="4">
+        <v>121</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>106</v>
+      </c>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1778</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1606,13 +1646,21 @@
       <c r="Z7" s="4">
         <v>141</v>
       </c>
-      <c r="AA7" s="4"/>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
+      <c r="AA7" s="4">
+        <v>104</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>112</v>
+      </c>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1828</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1694,13 +1742,21 @@
       <c r="Z8" s="4">
         <v>182</v>
       </c>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
+      <c r="AA8" s="4">
+        <v>127</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>120</v>
+      </c>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1955</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1782,13 +1838,21 @@
       <c r="Z9" s="4">
         <v>114</v>
       </c>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="4"/>
+      <c r="AA9" s="4">
+        <v>114</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>116</v>
+      </c>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1777</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1870,13 +1934,21 @@
       <c r="Z10" s="4">
         <v>138</v>
       </c>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
+      <c r="AA10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>63</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="4">
+        <v>107</v>
+      </c>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1700</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1958,13 +2030,21 @@
       <c r="Z11" s="4">
         <v>118</v>
       </c>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
+      <c r="AA11" s="4">
+        <v>121</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>53</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="4">
+        <v>111</v>
+      </c>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1363</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2046,13 +2126,21 @@
       <c r="Z12" s="4">
         <v>132</v>
       </c>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
+      <c r="AA12" s="4">
+        <v>117</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>122</v>
+      </c>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>1480</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2134,13 +2222,21 @@
       <c r="Z13" s="4">
         <v>156</v>
       </c>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="4">
+        <v>111</v>
+      </c>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1573</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2222,10 +2318,18 @@
       <c r="Z14" s="4">
         <v>134</v>
       </c>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
+      <c r="AA14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="4">
+        <v>0</v>
+      </c>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
         <v>1690</v>
@@ -2310,13 +2414,21 @@
       <c r="Z15" s="4">
         <v>0</v>
       </c>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
+      <c r="AA15" s="4">
+        <v>18</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>16</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>0</v>
+      </c>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>1215</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2398,13 +2510,21 @@
       <c r="Z16" s="4">
         <v>117</v>
       </c>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
+      <c r="AA16" s="4">
+        <v>117</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>104</v>
+      </c>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1760</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2486,13 +2606,21 @@
       <c r="Z17" s="4">
         <v>116</v>
       </c>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
+      <c r="AA17" s="4">
+        <v>117</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="4">
+        <v>101</v>
+      </c>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1812</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2574,13 +2702,21 @@
       <c r="Z18" s="4">
         <v>0</v>
       </c>
-      <c r="AA18" s="4"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
+      <c r="AA18" s="4">
+        <v>109</v>
+      </c>
+      <c r="AB18" s="4">
+        <v>26</v>
+      </c>
+      <c r="AC18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="4">
+        <v>108</v>
+      </c>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>1343</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2662,13 +2798,21 @@
       <c r="Z19" s="6">
         <v>2099</v>
       </c>
-      <c r="AA19" s="6"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
-      <c r="AD19" s="6"/>
+      <c r="AA19" s="6">
+        <v>1527</v>
+      </c>
+      <c r="AB19" s="6">
+        <v>186</v>
+      </c>
+      <c r="AC19" s="6">
+        <v>81</v>
+      </c>
+      <c r="AD19" s="6">
+        <v>1641</v>
+      </c>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>27441</v>
+        <v>30876</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2741,7 +2885,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>4.9705882352941178</v>
+        <v>5.2352941176470589</v>
       </c>
     </row>
   </sheetData>

--- a/Juni-2026.xlsx
+++ b/Juni-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F851B7F-7D87-4A8B-8BD2-59CB8D8E75A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F760D03-428D-4BBD-A2CB-4A61162E3B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -569,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>704</v>
+        <v>745</v>
       </c>
       <c r="C2" s="4">
-        <v>949</v>
+        <v>1030</v>
       </c>
       <c r="D2" s="9">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E2" s="13">
-        <v>5.6</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -588,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="C3" s="4">
-        <v>1334</v>
+        <v>1402</v>
       </c>
       <c r="D3" s="9">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E3" s="13">
-        <v>3.65</v>
+        <v>2.8571428571428572</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -613,10 +613,10 @@
         <v>1076</v>
       </c>
       <c r="D4" s="9">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E4" s="13">
-        <v>7.25</v>
+        <v>3.4285714285714284</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -626,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>716</v>
+        <v>736</v>
       </c>
       <c r="C5" s="4">
-        <v>894</v>
+        <v>936</v>
       </c>
       <c r="D5" s="9">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="E5" s="13">
-        <v>5.05</v>
+        <v>1.5238095238095237</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -645,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>664</v>
+        <v>693</v>
       </c>
       <c r="C6" s="4">
-        <v>1341</v>
+        <v>1416</v>
       </c>
       <c r="D6" s="9">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E6" s="13">
-        <v>5.4</v>
+        <v>3.9523809523809526</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -664,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>778</v>
+        <v>817</v>
       </c>
       <c r="C7" s="4">
-        <v>1266</v>
+        <v>1320</v>
       </c>
       <c r="D7" s="9">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="E7" s="13">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -683,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>882</v>
+        <v>923</v>
       </c>
       <c r="C8" s="4">
-        <v>1320</v>
+        <v>1385</v>
       </c>
       <c r="D8" s="9">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="E8" s="13">
-        <v>7.95</v>
+        <v>4.1904761904761907</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>730</v>
+        <v>760</v>
       </c>
       <c r="C9" s="4">
-        <v>1277</v>
+        <v>1364</v>
       </c>
       <c r="D9" s="9">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="E9" s="13">
-        <v>7.35</v>
+        <v>3.6190476190476191</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -721,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>819</v>
+        <v>856</v>
       </c>
       <c r="C10" s="4">
-        <v>1051</v>
+        <v>1128</v>
       </c>
       <c r="D10" s="9">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="E10" s="13">
-        <v>8.25</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -740,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C11" s="4">
-        <v>1243</v>
+        <v>1305</v>
       </c>
       <c r="D11" s="9">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E11" s="13">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -759,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>586</v>
+        <v>620</v>
       </c>
       <c r="C12" s="4">
-        <v>1133</v>
+        <v>1215</v>
       </c>
       <c r="D12" s="9">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="E12" s="13">
-        <v>3.95</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -778,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>472</v>
+        <v>501</v>
       </c>
       <c r="C13" s="4">
-        <v>1212</v>
+        <v>1280</v>
       </c>
       <c r="D13" s="9">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="E13" s="13">
-        <v>4.45</v>
+        <v>3.0476190476190474</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -797,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="C14" s="4">
-        <v>1099</v>
+        <v>1157</v>
       </c>
       <c r="D14" s="9">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="E14" s="13">
-        <v>3.8</v>
+        <v>2.0476190476190474</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -822,10 +822,10 @@
         <v>683</v>
       </c>
       <c r="D15" s="9">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E15" s="13">
-        <v>3.45</v>
+        <v>3.0952380952380953</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -835,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="C16" s="4">
-        <v>1393</v>
+        <v>1482</v>
       </c>
       <c r="D16" s="9">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="E16" s="13">
-        <v>4.05</v>
+        <v>2.1904761904761907</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -854,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="C17" s="4">
-        <v>1410</v>
+        <v>1488</v>
       </c>
       <c r="D17" s="9">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E17" s="13">
-        <v>4.05</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -873,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>627</v>
+        <v>657</v>
       </c>
       <c r="C18" s="4">
-        <v>959</v>
+        <v>1037</v>
       </c>
       <c r="D18" s="9">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E18" s="13">
-        <v>4.8499999999999996</v>
+        <v>4.4761904761904763</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -892,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>11236</v>
+        <v>11701</v>
       </c>
       <c r="C19" s="6">
-        <v>19640</v>
+        <v>20704</v>
       </c>
       <c r="D19" s="10">
-        <v>1780</v>
+        <v>1122</v>
       </c>
       <c r="E19" s="14">
-        <v>5.2352941176470589</v>
+        <v>3.1428571428571428</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1178,9 +1178,11 @@
       <c r="AD2" s="4">
         <v>110</v>
       </c>
-      <c r="AE2" s="4"/>
+      <c r="AE2" s="4">
+        <v>122</v>
+      </c>
       <c r="AF2" s="9">
-        <v>1653</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1274,9 +1276,11 @@
       <c r="AD3" s="4">
         <v>115</v>
       </c>
-      <c r="AE3" s="4"/>
+      <c r="AE3" s="4">
+        <v>98</v>
+      </c>
       <c r="AF3" s="9">
-        <v>1973</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1370,7 +1374,9 @@
       <c r="AD4" s="4">
         <v>99</v>
       </c>
-      <c r="AE4" s="4"/>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
       <c r="AF4" s="9">
         <v>1925</v>
       </c>
@@ -1466,9 +1472,11 @@
       <c r="AD5" s="4">
         <v>99</v>
       </c>
-      <c r="AE5" s="4"/>
+      <c r="AE5" s="4">
+        <v>62</v>
+      </c>
       <c r="AF5" s="9">
-        <v>1610</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1562,9 +1570,11 @@
       <c r="AD6" s="4">
         <v>106</v>
       </c>
-      <c r="AE6" s="4"/>
+      <c r="AE6" s="4">
+        <v>104</v>
+      </c>
       <c r="AF6" s="9">
-        <v>2005</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1658,9 +1668,11 @@
       <c r="AD7" s="4">
         <v>112</v>
       </c>
-      <c r="AE7" s="4"/>
+      <c r="AE7" s="4">
+        <v>93</v>
+      </c>
       <c r="AF7" s="9">
-        <v>2044</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1754,9 +1766,11 @@
       <c r="AD8" s="4">
         <v>120</v>
       </c>
-      <c r="AE8" s="4"/>
+      <c r="AE8" s="4">
+        <v>106</v>
+      </c>
       <c r="AF8" s="9">
-        <v>2202</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1850,9 +1864,11 @@
       <c r="AD9" s="4">
         <v>116</v>
       </c>
-      <c r="AE9" s="4"/>
+      <c r="AE9" s="4">
+        <v>117</v>
+      </c>
       <c r="AF9" s="9">
-        <v>2007</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1946,9 +1962,11 @@
       <c r="AD10" s="4">
         <v>107</v>
       </c>
-      <c r="AE10" s="4"/>
+      <c r="AE10" s="4">
+        <v>114</v>
+      </c>
       <c r="AF10" s="9">
-        <v>1870</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -2042,9 +2060,11 @@
       <c r="AD11" s="4">
         <v>111</v>
       </c>
-      <c r="AE11" s="4"/>
+      <c r="AE11" s="4">
+        <v>82</v>
+      </c>
       <c r="AF11" s="9">
-        <v>1648</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2138,9 +2158,11 @@
       <c r="AD12" s="4">
         <v>122</v>
       </c>
-      <c r="AE12" s="4"/>
+      <c r="AE12" s="4">
+        <v>116</v>
+      </c>
       <c r="AF12" s="9">
-        <v>1719</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2234,9 +2256,11 @@
       <c r="AD13" s="4">
         <v>111</v>
       </c>
-      <c r="AE13" s="4"/>
+      <c r="AE13" s="4">
+        <v>97</v>
+      </c>
       <c r="AF13" s="9">
-        <v>1684</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2330,9 +2354,11 @@
       <c r="AD14" s="4">
         <v>0</v>
       </c>
-      <c r="AE14" s="4"/>
+      <c r="AE14" s="4">
+        <v>93</v>
+      </c>
       <c r="AF14" s="9">
-        <v>1690</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2426,7 +2452,9 @@
       <c r="AD15" s="4">
         <v>0</v>
       </c>
-      <c r="AE15" s="4"/>
+      <c r="AE15" s="4">
+        <v>0</v>
+      </c>
       <c r="AF15" s="9">
         <v>1249</v>
       </c>
@@ -2522,9 +2550,11 @@
       <c r="AD16" s="4">
         <v>104</v>
       </c>
-      <c r="AE16" s="4"/>
+      <c r="AE16" s="4">
+        <v>115</v>
+      </c>
       <c r="AF16" s="9">
-        <v>1981</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2618,9 +2648,11 @@
       <c r="AD17" s="4">
         <v>101</v>
       </c>
-      <c r="AE17" s="4"/>
+      <c r="AE17" s="4">
+        <v>102</v>
+      </c>
       <c r="AF17" s="9">
-        <v>2030</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2714,9 +2746,11 @@
       <c r="AD18" s="4">
         <v>108</v>
       </c>
-      <c r="AE18" s="4"/>
+      <c r="AE18" s="4">
+        <v>108</v>
+      </c>
       <c r="AF18" s="9">
-        <v>1586</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2810,9 +2844,11 @@
       <c r="AD19" s="6">
         <v>1641</v>
       </c>
-      <c r="AE19" s="6"/>
+      <c r="AE19" s="6">
+        <v>1529</v>
+      </c>
       <c r="AF19" s="10">
-        <v>30876</v>
+        <v>32405</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2861,7 +2897,7 @@
       <c r="C34" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:AD18">
+  <conditionalFormatting sqref="B2:AE18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>99</formula>
     </cfRule>
@@ -2885,7 +2921,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>5.2352941176470589</v>
+        <v>3.1428571428571428</v>
       </c>
     </row>
   </sheetData>
